--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N101_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N101_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.83636706094059</v>
+        <v>12.16090964740285</v>
       </c>
       <c r="D2" t="n">
-        <v>67.35385825787728</v>
+        <v>10.94500196690506</v>
       </c>
       <c r="E2" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F2" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.92356528639188</v>
+        <v>9.73757935903868</v>
       </c>
       <c r="D3" t="n">
-        <v>48.32442446630896</v>
+        <v>7.852718975775207</v>
       </c>
       <c r="E3" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F3" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.28992411730233</v>
+        <v>9.147112669061629</v>
       </c>
       <c r="D4" t="n">
-        <v>35.9339672176619</v>
+        <v>5.839269672870059</v>
       </c>
       <c r="E4" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F4" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.3871347247841</v>
+        <v>9.975409392777417</v>
       </c>
       <c r="D5" t="n">
-        <v>29.5</v>
+        <v>4.79375</v>
       </c>
       <c r="E5" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F5" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>59.11544141054534</v>
+        <v>9.606259229213618</v>
       </c>
       <c r="D6" t="n">
-        <v>20.75486996466315</v>
+        <v>3.372666369257763</v>
       </c>
       <c r="E6" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F6" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63.15132198485117</v>
+        <v>10.26208982253831</v>
       </c>
       <c r="D7" t="n">
-        <v>18.00694310536911</v>
+        <v>2.92612825462248</v>
       </c>
       <c r="E7" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F7" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.6886640425885</v>
+        <v>9.211907906920631</v>
       </c>
       <c r="D8" t="n">
-        <v>14.4536865241615</v>
+        <v>2.348724060176243</v>
       </c>
       <c r="E8" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F8" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>62.19062696578975</v>
+        <v>10.10597688194084</v>
       </c>
       <c r="D9" t="n">
-        <v>36.35791393812482</v>
+        <v>5.908161014945284</v>
       </c>
       <c r="E9" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F9" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.6156774098522</v>
+        <v>8.712547579100983</v>
       </c>
       <c r="D10" t="n">
-        <v>53.02331739270893</v>
+        <v>8.616289076315201</v>
       </c>
       <c r="E10" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F10" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.13824568665403</v>
+        <v>9.93496492408128</v>
       </c>
       <c r="D11" t="n">
-        <v>61.26698543603031</v>
+        <v>9.955885133354926</v>
       </c>
       <c r="E11" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F11" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>56.84681195220363</v>
+        <v>9.237606942233091</v>
       </c>
       <c r="D12" t="n">
-        <v>56.35786449059454</v>
+        <v>9.158152979721612</v>
       </c>
       <c r="E12" t="n">
-        <v>5.324424032738226</v>
+        <v>0.8652189053199616</v>
       </c>
       <c r="F12" t="n">
-        <v>17.46052740786663</v>
+        <v>2.837335703778327</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
